--- a/output/intraday/riepilogo_intraday_2026-04-22.xlsx
+++ b/output/intraday/riepilogo_intraday_2026-04-22.xlsx
@@ -20,13 +20,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,12 +48,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -417,308 +429,378 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH8"/>
+  <dimension ref="A1:BV8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Ticker</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Gap%</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Market Cap</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Shs Float</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Shares Outstanding</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Change from Open</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Insider Ownership</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Institutional Ownership</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Short Float</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>VWAP_0930</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Volume</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>TimeHigh</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>TimeLow</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>OpenPM</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>HighPM</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>LowPM</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ClosePM</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>VolumePM</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>TimePMH</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>High_1m</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Low_1m</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Volume_1m</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Close_1m</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>High_5m</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>Low_5m</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Volume_5m</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Close_5m</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>High_15m</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>Low_15m</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Volume_15m</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Close_15m</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>High_30m</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Low_30m</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Volume_30m</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Close_30m</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>High_45m</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Low_45m</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Volume_45m</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Close_45m</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>High_60m</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>Low_60m</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>Volume_60m</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>Close_60m</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>High_90m</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>Low_90m</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>Volume_90m</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>Close_90m</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>High_120m</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>Low_120m</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>Volume_120m</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>Close_120m</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>High_240m</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>Low_240m</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>Volume_240m</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>Close_240m</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>High_5_15m</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>Low_5_15m</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>High_15_30m</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>Low_15_30m</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>High_30_45m</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>Low_30_45m</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>High_45_60m</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>Low_45_60m</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>High_60_90m</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>Low_60_90m</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>High_90_120m</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>Low_90_120m</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>High_120_240m</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>Low_120_240m</t>
         </is>
       </c>
     </row>
@@ -728,7 +810,7 @@
           <t>BIYA</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C2" t="n">
@@ -912,6 +994,48 @@
       </c>
       <c r="BH2" t="n">
         <v>1.26</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>1.11</v>
       </c>
     </row>
     <row r="3">
@@ -920,7 +1044,7 @@
           <t>CLIK</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C3" t="n">
@@ -1104,6 +1228,48 @@
       </c>
       <c r="BH3" t="n">
         <v>3.73</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>3.42</v>
       </c>
     </row>
     <row r="4">
@@ -1112,7 +1278,7 @@
           <t>EDBL</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C4" t="n">
@@ -1296,6 +1462,48 @@
       </c>
       <c r="BH4" t="n">
         <v>0.75</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>0.74</v>
       </c>
     </row>
     <row r="5">
@@ -1304,7 +1512,7 @@
           <t>LOBO</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C5" t="n">
@@ -1488,6 +1696,48 @@
       </c>
       <c r="BH5" t="n">
         <v>0.71</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0.68</v>
       </c>
     </row>
     <row r="6">
@@ -1496,7 +1746,7 @@
           <t>LOCL</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C6" t="n">
@@ -1680,6 +1930,48 @@
       </c>
       <c r="BH6" t="n">
         <v>2.73</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>2.64</v>
       </c>
     </row>
     <row r="7">
@@ -1688,7 +1980,7 @@
           <t>SPRC</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C7" t="n">
@@ -1872,6 +2164,48 @@
       </c>
       <c r="BH7" t="n">
         <v>5.1</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>5.03</v>
       </c>
     </row>
     <row r="8">
@@ -1880,7 +2214,7 @@
           <t>XRTX</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C8" t="n">
@@ -2062,6 +2396,48 @@
       </c>
       <c r="BH8" t="n">
         <v>2.68</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>2.61</v>
       </c>
     </row>
   </sheetData>

--- a/output/intraday/riepilogo_intraday_2026-04-22.xlsx
+++ b/output/intraday/riepilogo_intraday_2026-04-22.xlsx
@@ -1008,7 +1008,7 @@
         <v>1.17</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BN2" t="n">
         <v>1.12</v>
@@ -1233,16 +1233,16 @@
         <v>3.49</v>
       </c>
       <c r="BJ3" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="BK3" t="n">
         <v>3.45</v>
       </c>
       <c r="BL3" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="BM3" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="BN3" t="n">
         <v>3.27</v>
@@ -1251,7 +1251,7 @@
         <v>3.82</v>
       </c>
       <c r="BP3" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="BQ3" t="n">
         <v>3.9</v>
@@ -1470,7 +1470,7 @@
         <v>1.25</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="BL4" t="n">
         <v>1.08</v>
@@ -1482,7 +1482,7 @@
         <v>1.12</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BP4" t="n">
         <v>0.96</v>
@@ -1494,7 +1494,7 @@
         <v>0.88</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="BT4" t="n">
         <v>0.85</v>
@@ -1713,7 +1713,7 @@
         <v>0.77</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.57</v>
+        <v>0.63</v>
       </c>
       <c r="BO5" t="n">
         <v>0.79</v>
@@ -1938,7 +1938,7 @@
         <v>2.7</v>
       </c>
       <c r="BK6" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BL6" t="n">
         <v>2.61</v>
@@ -1962,7 +1962,7 @@
         <v>2.62</v>
       </c>
       <c r="BS6" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="BT6" t="n">
         <v>2.7</v>
@@ -2401,16 +2401,16 @@
         <v>3.36</v>
       </c>
       <c r="BJ8" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="BK8" t="n">
         <v>3.6</v>
       </c>
       <c r="BL8" t="n">
-        <v>2.99</v>
+        <v>3.05</v>
       </c>
       <c r="BM8" t="n">
-        <v>3.31</v>
+        <v>3.26</v>
       </c>
       <c r="BN8" t="n">
         <v>2.53</v>
